--- a/data/trans_orig/P78A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P78A_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona sustentadora principal ha trabajado anteriormente en 2023</t>
+          <t>Población según si la persona sustentadora principal ha trabajado anteriormente en 2023 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,7 +730,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>146144</t>
+          <t>145441</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>134398</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135486</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>280505</t>
+          <t>280939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,62 +878,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1593</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1088</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>9002</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1593</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>9436</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>147856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149253</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130732</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131832</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>281085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1186,97 +1186,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174238</t>
+          <t>174142</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97351</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98424</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>272879</t>
+          <t>272720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1534,7 +1534,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4598</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,62 +1564,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1073</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>4444</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>4285</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>462501</t>
+          <t>463862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>479789</t>
+          <t>479744</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>559917</t>
+          <t>559883</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1026161</t>
+          <t>1026903</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1044118</t>
+          <t>1044372</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,7%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20596</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4536</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21355</t>
+          <t>20613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>229091</t>
+          <t>228646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>236495</t>
+          <t>236492</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,7 +2117,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>476280</t>
+          <t>476450</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>707909</t>
+          <t>707601</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>716063</t>
+          <t>715926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,84%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8368</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>13451</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38989</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>280730</t>
+          <t>277576</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>328989</t>
+          <t>328690</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>296518</t>
+          <t>297600</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>360330</t>
+          <t>356483</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201042</t>
+          <t>201562</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226766</t>
+          <t>226580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>430813</t>
+          <t>431112</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>479072</t>
+          <t>482226</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>639504</t>
+          <t>643351</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>703316</t>
+          <t>702234</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,24%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1163519</t>
+          <t>1166150</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1254128</t>
+          <t>1253590</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1647406</t>
+          <t>1645879</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1844242</t>
+          <t>1844233</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2854406</t>
+          <t>2847221</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3053055</t>
+          <t>3029248</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>188907</t>
+          <t>189445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>279516</t>
+          <t>276885</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>325328</t>
+          <t>325337</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>522164</t>
+          <t>523691</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>559550</t>
+          <t>583357</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>758199</t>
+          <t>765384</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78A_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P78A_2023-Clase-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>152862</t>
+          <t>167338</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>145441</t>
+          <t>160042</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154455</t>
+          <t>168980</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>135486</t>
+          <t>154796</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>288348</t>
+          <t>322134</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>280939</t>
+          <t>316347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>289941</t>
+          <t>323776</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1593</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>7429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>154455</t>
+          <t>168980</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154455</t>
+          <t>168980</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154455</t>
+          <t>168980</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135486</t>
+          <t>154796</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135486</t>
+          <t>154796</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135486</t>
+          <t>154796</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>289941</t>
+          <t>323776</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>289941</t>
+          <t>323776</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>289941</t>
+          <t>323776</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>149253</t>
+          <t>162794</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>131832</t>
+          <t>151021</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>281085</t>
+          <t>313814</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>149253</t>
+          <t>162794</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>149253</t>
+          <t>162794</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>149253</t>
+          <t>162794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>131832</t>
+          <t>151021</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>131832</t>
+          <t>151021</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131832</t>
+          <t>151021</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281085</t>
+          <t>313814</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281085</t>
+          <t>313814</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281085</t>
+          <t>313814</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,27 +1411,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>177707</t>
+          <t>198962</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>174142</t>
+          <t>191771</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>178740</t>
+          <t>201184</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>98424</t>
+          <t>109916</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>276131</t>
+          <t>308878</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>272720</t>
+          <t>302810</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>277164</t>
+          <t>311100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>178740</t>
+          <t>201184</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>178740</t>
+          <t>201184</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>178740</t>
+          <t>201184</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>98424</t>
+          <t>109916</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98424</t>
+          <t>109916</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98424</t>
+          <t>109916</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>277164</t>
+          <t>311100</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>277164</t>
+          <t>311100</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>277164</t>
+          <t>311100</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>474772</t>
+          <t>510561</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>463862</t>
+          <t>499303</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>479744</t>
+          <t>516071</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>563286</t>
+          <t>395076</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>559883</t>
+          <t>392000</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>564419</t>
+          <t>396216</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1038058</t>
+          <t>905637</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1026903</t>
+          <t>895369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1044372</t>
+          <t>911273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3353</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>19679</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20613</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>483097</t>
+          <t>518982</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>483097</t>
+          <t>518982</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>483097</t>
+          <t>518982</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>564419</t>
+          <t>396216</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>564419</t>
+          <t>396216</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>564419</t>
+          <t>396216</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1047516</t>
+          <t>915198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1047516</t>
+          <t>915198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1047516</t>
+          <t>915198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>234354</t>
+          <t>257033</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>228646</t>
+          <t>252483</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>236492</t>
+          <t>259831</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,27 +2132,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>478979</t>
+          <t>531892</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>476450</t>
+          <t>528204</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>479607</t>
+          <t>532683</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>713332</t>
+          <t>788926</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>707601</t>
+          <t>784092</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>715926</t>
+          <t>791591</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>967</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8813</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>791</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>237459</t>
+          <t>259831</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>237459</t>
+          <t>259831</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>237459</t>
+          <t>259831</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>479607</t>
+          <t>532683</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>479607</t>
+          <t>532683</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>479607</t>
+          <t>532683</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>717065</t>
+          <t>792514</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>717065</t>
+          <t>792514</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>717065</t>
+          <t>792514</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24005</t>
+          <t>25057</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>40996</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>303497</t>
+          <t>321741</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>277576</t>
+          <t>294844</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>328690</t>
+          <t>348265</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>327502</t>
+          <t>346798</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>297600</t>
+          <t>318510</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>356483</t>
+          <t>381032</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,3%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>216026</t>
+          <t>211688</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>201562</t>
+          <t>195749</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>226580</t>
+          <t>222470</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>456305</t>
+          <t>520834</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>431112</t>
+          <t>494310</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>482226</t>
+          <t>547731</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>672332</t>
+          <t>732521</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>643351</t>
+          <t>698287</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>702234</t>
+          <t>760809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>70,49%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240031</t>
+          <t>236745</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240031</t>
+          <t>236745</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240031</t>
+          <t>236745</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>759802</t>
+          <t>842575</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759802</t>
+          <t>842575</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>759802</t>
+          <t>842575</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>999834</t>
+          <t>1079319</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>999834</t>
+          <t>1079319</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>999834</t>
+          <t>1079319</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1212952</t>
+          <t>1321745</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1166150</t>
+          <t>1277423</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1253590</t>
+          <t>1356807</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1711503</t>
+          <t>1664442</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1645879</t>
+          <t>1622427</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1844233</t>
+          <t>1699847</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2924455</t>
+          <t>2986187</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2847221</t>
+          <t>2928262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3029248</t>
+          <t>3040101</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>81,38%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>230083</t>
+          <t>226770</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>189445</t>
+          <t>191708</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>276885</t>
+          <t>271092</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>458067</t>
+          <t>522764</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>325337</t>
+          <t>487359</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>523691</t>
+          <t>564779</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>688150</t>
+          <t>749534</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>583357</t>
+          <t>695620</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>765384</t>
+          <t>807459</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1443035</t>
+          <t>1548515</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1443035</t>
+          <t>1548515</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1443035</t>
+          <t>1548515</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2169570</t>
+          <t>2187206</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2169570</t>
+          <t>2187206</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2169570</t>
+          <t>2187206</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3612605</t>
+          <t>3735721</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3612605</t>
+          <t>3735721</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3612605</t>
+          <t>3735721</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
